--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5436" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5436" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -813,6 +813,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -7579,7 +7583,7 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -7587,10 +7591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7616,10 +7620,10 @@
         <v>91</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7650,7 +7654,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7668,7 +7672,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7688,10 +7692,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7789,10 +7793,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7833,7 +7837,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -7892,10 +7896,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7995,10 +7999,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8098,10 +8102,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8201,10 +8205,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8304,10 +8308,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8405,10 +8409,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8506,10 +8510,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8609,10 +8613,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8712,10 +8716,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8815,10 +8819,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8841,13 +8845,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8898,7 +8902,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8918,10 +8922,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8944,7 +8948,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8977,7 +8981,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8995,7 +8999,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -9015,10 +9019,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9041,7 +9045,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -9094,7 +9098,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9114,10 +9118,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9140,13 +9144,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9177,7 +9181,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9195,7 +9199,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9215,10 +9219,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9244,10 +9248,10 @@
         <v>169</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9278,7 +9282,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9296,7 +9300,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9342,13 +9346,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9399,7 +9403,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9419,10 +9423,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9445,7 +9449,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9498,7 +9502,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9518,10 +9522,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9544,7 +9548,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9597,7 +9601,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9617,10 +9621,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9643,7 +9647,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9676,25 +9680,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9714,10 +9718,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9740,13 +9744,13 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9797,7 +9801,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -9817,10 +9821,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9918,10 +9922,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10019,10 +10023,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10120,10 +10124,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10221,10 +10225,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10324,10 +10328,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10427,10 +10431,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10530,10 +10534,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10633,10 +10637,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10734,10 +10738,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10771,7 +10775,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>74</v>
@@ -10793,7 +10797,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10811,7 +10815,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10831,10 +10835,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10857,7 +10861,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10910,7 +10914,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -10930,10 +10934,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10956,7 +10960,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -11009,7 +11013,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11029,10 +11033,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11055,7 +11059,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -11108,7 +11112,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11128,10 +11132,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11154,7 +11158,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -11207,7 +11211,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11227,10 +11231,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11253,7 +11257,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11306,7 +11310,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11326,10 +11330,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11352,7 +11356,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11405,7 +11409,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11425,10 +11429,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11451,7 +11455,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11504,7 +11508,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11524,10 +11528,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11550,7 +11554,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11591,7 +11595,7 @@
         <v>74</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -11601,7 +11605,7 @@
         <v>124</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11621,13 +11625,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>74</v>
@@ -11649,10 +11653,10 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -11704,7 +11708,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11724,10 +11728,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11825,10 +11829,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11926,10 +11930,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12027,10 +12031,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12128,10 +12132,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12231,10 +12235,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12334,10 +12338,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12437,10 +12441,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12540,10 +12544,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12641,10 +12645,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12681,7 +12685,7 @@
         <v>74</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>74</v>
@@ -12700,7 +12704,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -12718,7 +12722,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -12738,10 +12742,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12768,7 +12772,7 @@
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12819,7 +12823,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12839,10 +12843,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12869,12 +12873,12 @@
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
@@ -12920,7 +12924,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12940,10 +12944,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13019,7 +13023,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13039,10 +13043,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13065,7 +13069,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13118,7 +13122,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13138,10 +13142,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13164,7 +13168,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13217,7 +13221,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13237,10 +13241,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13263,7 +13267,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13316,7 +13320,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13336,10 +13340,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13362,7 +13366,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13415,7 +13419,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13435,10 +13439,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13461,7 +13465,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13514,7 +13518,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13534,10 +13538,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13560,7 +13564,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13613,7 +13617,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13633,10 +13637,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13659,7 +13663,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13712,7 +13716,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13732,10 +13736,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13758,7 +13762,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13811,7 +13815,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13831,10 +13835,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13857,7 +13861,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13910,7 +13914,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13930,10 +13934,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13956,7 +13960,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14009,7 +14013,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14029,10 +14033,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14055,7 +14059,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14108,7 +14112,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14128,13 +14132,13 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>74</v>
@@ -14156,10 +14160,10 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -14211,7 +14215,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14231,10 +14235,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14332,10 +14336,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14433,10 +14437,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14534,10 +14538,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14635,10 +14639,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14738,10 +14742,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14841,10 +14845,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14944,10 +14948,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15047,10 +15051,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15148,10 +15152,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15188,7 +15192,7 @@
         <v>74</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>74</v>
@@ -15207,7 +15211,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -15225,7 +15229,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -15245,10 +15249,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15275,7 +15279,7 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15326,7 +15330,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15346,10 +15350,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15376,12 +15380,12 @@
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
@@ -15427,7 +15431,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15447,10 +15451,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15526,7 +15530,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15546,10 +15550,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15572,7 +15576,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15625,7 +15629,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15645,10 +15649,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15671,7 +15675,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15724,7 +15728,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15744,10 +15748,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15770,7 +15774,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15823,7 +15827,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15843,10 +15847,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15869,7 +15873,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15922,7 +15926,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15942,10 +15946,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15968,7 +15972,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16021,7 +16025,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16041,10 +16045,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16067,7 +16071,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16120,7 +16124,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16140,10 +16144,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16166,7 +16170,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16219,7 +16223,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16239,10 +16243,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16265,7 +16269,7 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16318,7 +16322,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16338,10 +16342,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16364,7 +16368,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16417,7 +16421,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16437,10 +16441,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16463,7 +16467,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16516,7 +16520,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16536,10 +16540,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16562,7 +16566,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16615,7 +16619,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16635,13 +16639,13 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>74</v>
@@ -16663,10 +16667,10 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -16718,7 +16722,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16738,10 +16742,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16839,10 +16843,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16940,10 +16944,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17041,10 +17045,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17142,10 +17146,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17245,10 +17249,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17348,10 +17352,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17451,10 +17455,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17554,10 +17558,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17655,10 +17659,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17695,7 +17699,7 @@
         <v>74</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>74</v>
@@ -17714,7 +17718,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>74</v>
@@ -17732,7 +17736,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -17752,10 +17756,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17782,7 +17786,7 @@
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17833,7 +17837,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17853,10 +17857,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17883,12 +17887,12 @@
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
@@ -17934,7 +17938,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17954,10 +17958,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18033,7 +18037,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18053,10 +18057,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18079,7 +18083,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18132,7 +18136,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18152,10 +18156,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18178,7 +18182,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18231,7 +18235,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18251,10 +18255,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18277,7 +18281,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18330,7 +18334,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18350,10 +18354,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18376,7 +18380,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18429,7 +18433,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18449,10 +18453,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18475,7 +18479,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18528,7 +18532,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18548,10 +18552,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18574,7 +18578,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -18627,7 +18631,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -18647,10 +18651,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18673,7 +18677,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18726,7 +18730,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18746,10 +18750,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18772,7 +18776,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -18825,7 +18829,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -18845,10 +18849,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18871,7 +18875,7 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -18924,7 +18928,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -18944,10 +18948,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18970,7 +18974,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19023,7 +19027,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19043,10 +19047,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19069,7 +19073,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19122,7 +19126,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -19142,10 +19146,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19168,7 +19172,7 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19221,7 +19225,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -19241,10 +19245,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19267,7 +19271,7 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19320,7 +19324,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -19340,10 +19344,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19366,7 +19370,7 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19419,7 +19423,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
